--- a/ATR_Tracker_Dashboard.xlsx
+++ b/ATR_Tracker_Dashboard.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,6 +468,2119 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>72001.046875</v>
+      </c>
+      <c r="E2" t="n">
+        <v>75766.36827238886</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1801.07388530818</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.93365241625565</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-1.741688487669008</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-2.090597963861201</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-4.96964746132756</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>72001.046875</v>
+      </c>
+      <c r="E3" t="n">
+        <v>76346.66638509305</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6092.519762037029</v>
+      </c>
+      <c r="G3" t="n">
+        <v>41.51124112173228</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5340390808570523</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.7132713031430684</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-5.691957115944942</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1976.2900390625</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2100.838204314618</v>
+      </c>
+      <c r="F4" t="n">
+        <v>66.83703767315005</v>
+      </c>
+      <c r="G4" t="n">
+        <v>29.35468788658376</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-1.367225757534329</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-1.863460284718032</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-5.928498681922574</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1976.2900390625</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2279.26631872778</v>
+      </c>
+      <c r="F5" t="n">
+        <v>253.0892608908958</v>
+      </c>
+      <c r="G5" t="n">
+        <v>33.9475220087983</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2888917433428367</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-1.197112349211412</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-13.29271078047575</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SOL</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>80.48000335693359</v>
+      </c>
+      <c r="E6" t="n">
+        <v>84.57659785917735</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.819571299886665</v>
+      </c>
+      <c r="G6" t="n">
+        <v>35.74836904597659</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-1.533459611685499</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-1.452913959795387</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-4.843650141927815</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SOL</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>80.48000335693359</v>
+      </c>
+      <c r="E7" t="n">
+        <v>92.62064758492545</v>
+      </c>
+      <c r="F7" t="n">
+        <v>11.93833715767707</v>
+      </c>
+      <c r="G7" t="n">
+        <v>35.20957367311867</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.8315787751010267</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-1.016946000740538</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-13.10792414494824</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>XLM</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.2627870142459869</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.1882957779661356</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.0202969665904604</v>
+      </c>
+      <c r="G8" t="n">
+        <v>74.94159447449269</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.471510663537873</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.670067443223872</v>
+      </c>
+      <c r="J8" t="n">
+        <v>39.5607575934328</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>XLM</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.2627870142459869</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1883245521627999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.03176939447053215</v>
+      </c>
+      <c r="G9" t="n">
+        <v>67.95947416080321</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.30629307913332</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.343842661283805</v>
+      </c>
+      <c r="J9" t="n">
+        <v>39.53943403981491</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>REZ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.003990000113844872</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.004559591481567672</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.0003282417333037169</v>
+      </c>
+      <c r="G10" t="n">
+        <v>33.70981719967634</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.9698931738179873</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1.73528016072157</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-12.49215790549211</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>REZ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.003990000113844872</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.004375402328113554</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.001054739256166453</v>
+      </c>
+      <c r="G11" t="n">
+        <v>46.54856267646955</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.5381186343540172</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.3654004646318584</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-8.808383443788312</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>RSR</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.00158100004773587</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.001710562891771325</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.0001096592384376386</v>
+      </c>
+      <c r="G12" t="n">
+        <v>37.86237420720877</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-1.133311973823171</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-1.181504138469242</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-7.574281229805601</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>RSR</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.00158100004773587</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.001878667390949833</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.0003448388348496248</v>
+      </c>
+      <c r="G13" t="n">
+        <v>38.03887173755143</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.7816416242288563</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.8632071365853209</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-15.84460052098237</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NEAR</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2.302999973297119</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.097837184107503</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1920363425323165</v>
+      </c>
+      <c r="G14" t="n">
+        <v>61.75672776962445</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.751155387729926</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.068353971358783</v>
+      </c>
+      <c r="J14" t="n">
+        <v>9.779728891443963</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NEAR</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2.302999973297119</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.622396763831212</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3007102381429618</v>
+      </c>
+      <c r="G15" t="n">
+        <v>70.85432247465855</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.623887754344853</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.263319046497976</v>
+      </c>
+      <c r="J15" t="n">
+        <v>41.95047873854827</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ONDO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.3505699932575226</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.374904528082169</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.03359933560800073</v>
+      </c>
+      <c r="G16" t="n">
+        <v>45.92730082513985</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-1.633477067649114</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.724256429012596</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-6.490861806639181</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ONDO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.3505699932575226</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.3330284212700577</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.07002761509811456</v>
+      </c>
+      <c r="G17" t="n">
+        <v>51.27125756647683</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.154382717118016</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2504950648810146</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5.26728977682064</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ACH</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.006111000198870897</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.006720577091762051</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.0003654610797028256</v>
+      </c>
+      <c r="G18" t="n">
+        <v>33.8236086660237</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-1.088056993981048</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-1.66796665020207</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-9.070305787256887</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ACH</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.006111000198870897</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.007174078507591003</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.001146521949158175</v>
+      </c>
+      <c r="G19" t="n">
+        <v>41.19351954926027</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.1885140537725472</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-0.9272201980089988</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-14.81832555352226</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BNB</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>691.3900146484375</v>
+      </c>
+      <c r="E20" t="n">
+        <v>663.0554927984483</v>
+      </c>
+      <c r="F20" t="n">
+        <v>23.18437474867704</v>
+      </c>
+      <c r="G20" t="n">
+        <v>60.2109567415424</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5023852616982728</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.222138710107161</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.273325861520635</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BNB</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>691.3900146484375</v>
+      </c>
+      <c r="E21" t="n">
+        <v>687.4174075747648</v>
+      </c>
+      <c r="F21" t="n">
+        <v>58.16384592879493</v>
+      </c>
+      <c r="G21" t="n">
+        <v>47.66011348653202</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.596955604502457</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.06830028190598114</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.5779031822438508</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>XRP</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1.299900054931641</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.354815897877998</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.04188255766581428</v>
+      </c>
+      <c r="G22" t="n">
+        <v>36.76643097299292</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-1.105671791296424</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-1.311186470142002</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-4.053380465373242</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>XRP</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1.299900054931641</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.480131916453963</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.1617461956009325</v>
+      </c>
+      <c r="G23" t="n">
+        <v>32.22472301217438</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.5915698304674747</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-1.11428810336287</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-12.17674313476832</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MSTR</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>159.0899963378906</v>
+      </c>
+      <c r="E24" t="n">
+        <v>165.6432765409464</v>
+      </c>
+      <c r="F24" t="n">
+        <v>10.05101757149238</v>
+      </c>
+      <c r="G24" t="n">
+        <v>45.80059865335512</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.9317468234679487</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.6520016661440096</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-3.956260911945801</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MSTR</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>159.0899963378906</v>
+      </c>
+      <c r="E25" t="n">
+        <v>157.7584079740834</v>
+      </c>
+      <c r="F25" t="n">
+        <v>20.75390697719308</v>
+      </c>
+      <c r="G25" t="n">
+        <v>50.33652083447394</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.7012562434627623</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.06416085247325014</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.8440680791010492</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>XXI</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>7.320000171661377</v>
+      </c>
+      <c r="E26" t="n">
+        <v>7.72095925672574</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.4215395232243465</v>
+      </c>
+      <c r="G26" t="n">
+        <v>42.43164778670099</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-1.006800106809123</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.9511779156493697</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-5.193125254677219</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>XXI</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>7.320000171661377</v>
+      </c>
+      <c r="E27" t="n">
+        <v>8.202233011655117</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.911029692655893</v>
+      </c>
+      <c r="G27" t="n">
+        <v>39.30355722969962</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.9712821879034578</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.4616531304480357</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-10.75600801318513</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>RIOT</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>27.11000061035156</v>
+      </c>
+      <c r="E28" t="n">
+        <v>23.66375450580085</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.469158740934135</v>
+      </c>
+      <c r="G28" t="n">
+        <v>70.74909986291973</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.3199334488289517</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.345727530000933</v>
+      </c>
+      <c r="J28" t="n">
+        <v>14.56339527062753</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>RIOT</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>27.11000061035156</v>
+      </c>
+      <c r="E29" t="n">
+        <v>18.63309915584929</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.82688010137877</v>
+      </c>
+      <c r="G29" t="n">
+        <v>78.13635766156609</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.533523121832533</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.998677393628329</v>
+      </c>
+      <c r="J29" t="n">
+        <v>45.49378170319677</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MARA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>14.38000011444092</v>
+      </c>
+      <c r="E30" t="n">
+        <v>13.00065160015771</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.9050392540672604</v>
+      </c>
+      <c r="G30" t="n">
+        <v>67.20262219367305</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.7770431029022761</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.52407589845898</v>
+      </c>
+      <c r="J30" t="n">
+        <v>10.60984138876909</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MARA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>14.38000011444092</v>
+      </c>
+      <c r="E31" t="n">
+        <v>11.11326720758472</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.678021862044484</v>
+      </c>
+      <c r="G31" t="n">
+        <v>69.0090102223966</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.541840024684614</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.946776130125055</v>
+      </c>
+      <c r="J31" t="n">
+        <v>29.39489212161371</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>IREN</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>63.54000091552734</v>
+      </c>
+      <c r="E32" t="n">
+        <v>56.08550110971867</v>
+      </c>
+      <c r="F32" t="n">
+        <v>4.947737291384147</v>
+      </c>
+      <c r="G32" t="n">
+        <v>60.42859426857206</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2342949864207764</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.506648265013935</v>
+      </c>
+      <c r="J32" t="n">
+        <v>13.29131354505618</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>IREN</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>63.54000091552734</v>
+      </c>
+      <c r="E33" t="n">
+        <v>48.32386758392506</v>
+      </c>
+      <c r="F33" t="n">
+        <v>9.555918227670446</v>
+      </c>
+      <c r="G33" t="n">
+        <v>63.8999778387233</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.7738927345354099</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.592325611111021</v>
+      </c>
+      <c r="J33" t="n">
+        <v>31.48782184119703</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BMNR</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>19.27000045776367</v>
+      </c>
+      <c r="E34" t="n">
+        <v>20.22558996351397</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.209195540639395</v>
+      </c>
+      <c r="G34" t="n">
+        <v>42.50919705166537</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-0.5587234711602452</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-0.7902687974229594</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-4.724655782472301</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BMNR</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>19.27000045776367</v>
+      </c>
+      <c r="E35" t="n">
+        <v>22.68376308758678</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3.422119929380746</v>
+      </c>
+      <c r="G35" t="n">
+        <v>34.64249370253906</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.5462020360118556</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-0.9975578589499782</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-15.04936644172244</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>HUT</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>124.8300018310547</v>
+      </c>
+      <c r="E36" t="n">
+        <v>101.9549643252501</v>
+      </c>
+      <c r="F36" t="n">
+        <v>8.571867865972264</v>
+      </c>
+      <c r="G36" t="n">
+        <v>74.31282900105137</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.8912837096348716</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2.66861760627594</v>
+      </c>
+      <c r="J36" t="n">
+        <v>22.43641362359766</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>HUT</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>124.8300018310547</v>
+      </c>
+      <c r="E37" t="n">
+        <v>73.49973087353807</v>
+      </c>
+      <c r="F37" t="n">
+        <v>13.08996357521593</v>
+      </c>
+      <c r="G37" t="n">
+        <v>92.40774627479144</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.25779852567344</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3.921345591419636</v>
+      </c>
+      <c r="J37" t="n">
+        <v>69.8373590589526</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>WULF</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>25.55999946594238</v>
+      </c>
+      <c r="E38" t="n">
+        <v>23.24188538415398</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.711759166497312</v>
+      </c>
+      <c r="G38" t="n">
+        <v>61.96907291860929</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.2032339878142826</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.35422910369561</v>
+      </c>
+      <c r="J38" t="n">
+        <v>9.973864183018723</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>WULF</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>25.55999946594238</v>
+      </c>
+      <c r="E39" t="n">
+        <v>18.63900267582508</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.938211660971429</v>
+      </c>
+      <c r="G39" t="n">
+        <v>76.51720165363062</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.458993658097611</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2.355513349174134</v>
+      </c>
+      <c r="J39" t="n">
+        <v>37.13179782464376</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>HIVE</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>4.519999980926514</v>
+      </c>
+      <c r="E40" t="n">
+        <v>3.483955554259131</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.3566187505366081</v>
+      </c>
+      <c r="G40" t="n">
+        <v>77.64085530636912</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.507979904076257</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2.905187753331635</v>
+      </c>
+      <c r="J40" t="n">
+        <v>29.73759023420435</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HIVE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>4.519999980926514</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2.817182904073446</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.4909582410718644</v>
+      </c>
+      <c r="G41" t="n">
+        <v>76.15281877359256</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.967830401959408</v>
+      </c>
+      <c r="I41" t="n">
+        <v>3.468354198791861</v>
+      </c>
+      <c r="J41" t="n">
+        <v>60.44396600557653</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CLSK</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>18.29000091552734</v>
+      </c>
+      <c r="E42" t="n">
+        <v>15.04100676488465</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.123766249592996</v>
+      </c>
+      <c r="G42" t="n">
+        <v>77.62553698475767</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.642110494089415</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2.891165446390123</v>
+      </c>
+      <c r="J42" t="n">
+        <v>21.60090877844642</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CLSK</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>18.29000091552734</v>
+      </c>
+      <c r="E43" t="n">
+        <v>12.58968628127141</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.138824856549421</v>
+      </c>
+      <c r="G43" t="n">
+        <v>71.82915423881768</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.867503307125546</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2.665161954145366</v>
+      </c>
+      <c r="J43" t="n">
+        <v>45.27765431880384</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SLNH</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1.700000047683716</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.712619252318634</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.2628225001237786</v>
+      </c>
+      <c r="G44" t="n">
+        <v>51.68495652472369</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-1.523673968021653</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-0.0480141716518759</v>
+      </c>
+      <c r="J44" t="n">
+        <v>-0.7368365512552622</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SLNH</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1.700000047683716</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.361547986944075</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.4465776651930053</v>
+      </c>
+      <c r="G45" t="n">
+        <v>58.2248636999797</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.057000200038632</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.7578795070133346</v>
+      </c>
+      <c r="J45" t="n">
+        <v>24.85788705099401</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>MSTY</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>6.730000019073486</v>
+      </c>
+      <c r="E46" t="n">
+        <v>7.021260413751772</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.4535622862773057</v>
+      </c>
+      <c r="G46" t="n">
+        <v>44.68646824284213</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-0.9673280995337931</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-0.6421618452205499</v>
+      </c>
+      <c r="J46" t="n">
+        <v>-4.148263666560866</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>MSTY</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v/>
+      </c>
+      <c r="E47" t="n">
+        <v>6.881703635229012</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.324665923677588</v>
+      </c>
+      <c r="G47" t="n">
+        <v>47.57279325185998</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.7302432273183066</v>
+      </c>
+      <c r="J47" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>YMST</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>8.502499580383301</v>
+      </c>
+      <c r="E48" t="n">
+        <v>9.66020157177458</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.4456390168030242</v>
+      </c>
+      <c r="G48" t="n">
+        <v>37.7078939474617</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-1.608519813055622</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-2.59784701908853</v>
+      </c>
+      <c r="J48" t="n">
+        <v>-11.9842425935902</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>YMST</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v/>
+      </c>
+      <c r="E49" t="n">
+        <v>9.318927986926848</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.069146096025437</v>
+      </c>
+      <c r="G49" t="n">
+        <v>50.12014066130152</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.5283678823589186</v>
+      </c>
+      <c r="J49" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>MARY</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>13.07499980926514</v>
+      </c>
+      <c r="E50" t="n">
+        <v>12.60347900599985</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.4775843797685067</v>
+      </c>
+      <c r="G50" t="n">
+        <v>56.76485690162703</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-1.395281149226666</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.9873036540555116</v>
+      </c>
+      <c r="J50" t="n">
+        <v>3.741195609885299</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>MARY</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v/>
+      </c>
+      <c r="E51" t="n">
+        <v>10.0396551035204</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1.036620634042273</v>
+      </c>
+      <c r="G51" t="n">
+        <v>91.73694150948708</v>
+      </c>
+      <c r="H51" t="n">
+        <v/>
+      </c>
+      <c r="J51" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>RIOY</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>12.05500030517578</v>
+      </c>
+      <c r="E52" t="n">
+        <v>11.73471702173637</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.5189957177948873</v>
+      </c>
+      <c r="G52" t="n">
+        <v>55.3306599324749</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-1.968358458470681</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.617121244853877</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2.729365206217989</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>RIOY</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v/>
+      </c>
+      <c r="E53" t="n">
+        <v>9.400787352855257</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.194455708156203</v>
+      </c>
+      <c r="G53" t="n">
+        <v>97.68451508929084</v>
+      </c>
+      <c r="H53" t="n">
+        <v/>
+      </c>
+      <c r="J53" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>IREY</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>9.237500190734863</v>
+      </c>
+      <c r="E54" t="n">
+        <v>10.31506661361132</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.6124284005416278</v>
+      </c>
+      <c r="G54" t="n">
+        <v>43.81707904615913</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-1.969454005076276</v>
+      </c>
+      <c r="I54" t="n">
+        <v>-1.759497799127972</v>
+      </c>
+      <c r="J54" t="n">
+        <v>-10.4465289778599</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>IREY</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v/>
+      </c>
+      <c r="E55" t="n">
+        <v>8.667091027090382</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.8624335572798643</v>
+      </c>
+      <c r="G55" t="n">
+        <v>88.39881348364079</v>
+      </c>
+      <c r="H55" t="n">
+        <v/>
+      </c>
+      <c r="J55" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BMNY</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>9.158749580383301</v>
+      </c>
+      <c r="E56" t="n">
+        <v>9.270461510372634</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.2362707776994474</v>
+      </c>
+      <c r="G56" t="n">
+        <v>48.06401886444286</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-0.453753447332806</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-0.4728131471740379</v>
+      </c>
+      <c r="J56" t="n">
+        <v>-1.205030945485721</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BMNY</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>9.158749580383301</v>
+      </c>
+      <c r="E57" t="n">
+        <v>8.767205523498239</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.5376730112833533</v>
+      </c>
+      <c r="G57" t="n">
+        <v>60.19344326541734</v>
+      </c>
+      <c r="H57" t="n">
+        <v/>
+      </c>
+      <c r="I57" t="n">
+        <v>0.7282196589159247</v>
+      </c>
+      <c r="J57" t="n">
+        <v>4.466007507587549</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ATR_Tracker_Dashboard.xlsx
+++ b/ATR_Tracker_Dashboard.xlsx
@@ -2194,9 +2194,6 @@
           <t>1w</t>
         </is>
       </c>
-      <c r="D47" t="n">
-        <v/>
-      </c>
       <c r="E47" t="n">
         <v>6.881703635229012</v>
       </c>
@@ -2209,9 +2206,6 @@
       <c r="H47" t="n">
         <v>0.7302432273183066</v>
       </c>
-      <c r="J47" t="n">
-        <v/>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2267,9 +2261,6 @@
           <t>1w</t>
         </is>
       </c>
-      <c r="D49" t="n">
-        <v/>
-      </c>
       <c r="E49" t="n">
         <v>9.318927986926848</v>
       </c>
@@ -2282,9 +2273,6 @@
       <c r="H49" t="n">
         <v>0.5283678823589186</v>
       </c>
-      <c r="J49" t="n">
-        <v/>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2340,9 +2328,6 @@
           <t>1w</t>
         </is>
       </c>
-      <c r="D51" t="n">
-        <v/>
-      </c>
       <c r="E51" t="n">
         <v>10.0396551035204</v>
       </c>
@@ -2352,12 +2337,6 @@
       <c r="G51" t="n">
         <v>91.73694150948708</v>
       </c>
-      <c r="H51" t="n">
-        <v/>
-      </c>
-      <c r="J51" t="n">
-        <v/>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2413,9 +2392,6 @@
           <t>1w</t>
         </is>
       </c>
-      <c r="D53" t="n">
-        <v/>
-      </c>
       <c r="E53" t="n">
         <v>9.400787352855257</v>
       </c>
@@ -2425,12 +2401,6 @@
       <c r="G53" t="n">
         <v>97.68451508929084</v>
       </c>
-      <c r="H53" t="n">
-        <v/>
-      </c>
-      <c r="J53" t="n">
-        <v/>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2486,9 +2456,6 @@
           <t>1w</t>
         </is>
       </c>
-      <c r="D55" t="n">
-        <v/>
-      </c>
       <c r="E55" t="n">
         <v>8.667091027090382</v>
       </c>
@@ -2498,12 +2465,6 @@
       <c r="G55" t="n">
         <v>88.39881348364079</v>
       </c>
-      <c r="H55" t="n">
-        <v/>
-      </c>
-      <c r="J55" t="n">
-        <v/>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2570,9 +2531,6 @@
       </c>
       <c r="G57" t="n">
         <v>60.19344326541734</v>
-      </c>
-      <c r="H57" t="n">
-        <v/>
       </c>
       <c r="I57" t="n">
         <v>0.7282196589159247</v>
